--- a/seo_forms/018_submit_your_project_here--seo_forms.xlsx
+++ b/seo_forms/018_submit_your_project_here--seo_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -525,13 +525,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Submit</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Project Title</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Enter a brief title for your project</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -548,13 +552,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Project Description</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Briefly describe your project</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,7 +574,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>project_status_1</t>
+          <t>project_status</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -574,10 +582,14 @@
           <t>Status</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Select the current status of your project</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -594,13 +606,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Project Status 2</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Select the next expected status of your project</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -617,36 +633,44 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Project Status 3</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Select the reason for project completion</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>project_status_4</t>
+          <t>project_submitter</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Submitter</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Enter the name of the person submitting the project</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -658,16 +682,135 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>submitter</t>
+          <t>submitter_email</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Submitter</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Enter the submitter's email address</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>submission_date</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Submission Date</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>submission_time</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Submission Time</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>select_multiple</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>project_tags</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Tags</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>project_comments</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Comments</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>project_submission</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Submission</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -684,12 +827,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -712,24 +855,24 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>project_status_1_choices</t>
+          <t>project_status_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>draft</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Draft</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>project_status_1_choices</t>
+          <t>project_status_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -746,7 +889,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>project_status_1_choices</t>
+          <t>project_status_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -768,12 +911,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -785,12 +928,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -802,12 +945,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
@@ -819,12 +962,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>completed_due_to_success</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Completed due to success</t>
         </is>
       </c>
     </row>
@@ -836,46 +979,63 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>completed_due_to_failure</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Completed due to failure</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>project_status_4_choices</t>
+          <t>project_tags_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>technology</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Technology</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>project_status_4_choices</t>
+          <t>project_tags_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>inactive</t>
+          <t>software_development</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Inactive</t>
+          <t>Software Development</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>project_tags_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>project_management</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Project Management</t>
         </is>
       </c>
     </row>
